--- a/AAII_Financials/Yearly/ROG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ROG_YR_FIN.xlsx
@@ -1059,10 +1059,10 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>54300</v>
+        <v>52900</v>
       </c>
       <c r="E15" s="3">
-        <v>49400</v>
+        <v>47100</v>
       </c>
       <c r="F15" s="3">
         <v>51100</v>
@@ -1302,10 +1302,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>103900</v>
+        <v>102500</v>
       </c>
       <c r="E21" s="3">
-        <v>107500</v>
+        <v>105200</v>
       </c>
       <c r="F21" s="3">
         <v>120300</v>
@@ -4090,10 +4090,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>43300</v>
+        <v>41900</v>
       </c>
       <c r="E83" s="3">
-        <v>37000</v>
+        <v>34700</v>
       </c>
       <c r="F83" s="3">
         <v>37700</v>
